--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -86,16 +86,16 @@
     <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydneyroosters</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
     <t xml:space="preserve">canterburybulldogs</t>
@@ -585,34 +585,34 @@
         <v>3.61</v>
       </c>
       <c r="J2" t="n">
-        <v>97.6</v>
+        <v>97.7</v>
       </c>
       <c r="K2" t="n">
         <v>1.02</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>42.46</v>
+        <v>42.83</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="O2" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="P2" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R2" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="S2" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="T2"/>
     </row>
@@ -633,46 +633,46 @@
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="G3" t="n">
         <v>1.35</v>
       </c>
       <c r="H3" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="J3" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="K3" t="n">
         <v>1.02</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>44.54</v>
+        <v>44.25</v>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="O3" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="P3" t="n">
         <v>38.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R3" t="n">
         <v>20.3</v>
       </c>
       <c r="S3" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="T3"/>
     </row>
@@ -687,52 +687,52 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="F4" t="n">
-        <v>79.2</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="H4" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>4.81</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>98.7</v>
+        <v>98.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="n">
-        <v>79.68</v>
+        <v>52.91</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="O4" t="n">
-        <v>4.01</v>
+        <v>3.86</v>
       </c>
       <c r="P4" t="n">
-        <v>36.5</v>
+        <v>35.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="T4"/>
     </row>
@@ -747,52 +747,52 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="E5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F5" t="n">
-        <v>75.2</v>
+        <v>78.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="H5" t="n">
-        <v>24.8</v>
+        <v>21.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.04</v>
+        <v>4.71</v>
       </c>
       <c r="J5" t="n">
-        <v>98.1</v>
+        <v>98.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>53.76</v>
+        <v>76.92</v>
       </c>
       <c r="N5" t="n">
-        <v>25.9</v>
+        <v>24.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.86</v>
+        <v>4.07</v>
       </c>
       <c r="P5" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="S5" t="n">
-        <v>6.07</v>
+        <v>6.11</v>
       </c>
       <c r="T5"/>
     </row>
@@ -813,46 +813,46 @@
         <v>5.7</v>
       </c>
       <c r="F6" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="H6" t="n">
-        <v>74.4</v>
+        <v>74.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J6" t="n">
         <v>84.4</v>
       </c>
       <c r="K6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="L6" t="n">
         <v>15.6</v>
       </c>
       <c r="M6" t="n">
-        <v>6.42</v>
+        <v>6.39</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>80</v>
+        <v>79.68</v>
       </c>
       <c r="P6" t="n">
         <v>14.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="R6" t="n">
         <v>7.7</v>
       </c>
       <c r="S6" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="T6"/>
     </row>
@@ -867,52 +867,52 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F7" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="H7" t="n">
-        <v>74.6</v>
+        <v>74.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J7" t="n">
-        <v>77.4</v>
+        <v>77.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="M7" t="n">
-        <v>4.43</v>
+        <v>4.51</v>
       </c>
       <c r="N7" t="n">
         <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>53.91</v>
+        <v>51.95</v>
       </c>
       <c r="P7" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.59</v>
+        <v>8.33</v>
       </c>
       <c r="R7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="S7" t="n">
-        <v>17.56</v>
+        <v>16.84</v>
       </c>
       <c r="T7"/>
     </row>
@@ -933,40 +933,40 @@
         <v>5.5</v>
       </c>
       <c r="F8" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="H8" t="n">
-        <v>71.5</v>
+        <v>71.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J8" t="n">
-        <v>80.9</v>
+        <v>80.8</v>
       </c>
       <c r="K8" t="n">
         <v>1.24</v>
       </c>
       <c r="L8" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="M8" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
         <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>43.01</v>
+        <v>42.92</v>
       </c>
       <c r="P8" t="n">
         <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.3</v>
+        <v>8.36</v>
       </c>
       <c r="R8" t="n">
         <v>5.4</v>
@@ -987,52 +987,52 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>4.9</v>
       </c>
       <c r="F9" t="n">
-        <v>8.9</v>
+        <v>9.2</v>
       </c>
       <c r="G9" t="n">
-        <v>11.18</v>
+        <v>10.83</v>
       </c>
       <c r="H9" t="n">
-        <v>91.1</v>
+        <v>90.8</v>
       </c>
       <c r="I9" t="n">
         <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="L9" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="N9" t="n">
         <v>0.4</v>
       </c>
       <c r="O9" t="n">
-        <v>263.16</v>
+        <v>246.91</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.16</v>
+        <v>19.63</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>42.74</v>
+        <v>41.67</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1056,7 +1056,7 @@
         <v>6.4</v>
       </c>
       <c r="G10" t="n">
-        <v>15.7</v>
+        <v>15.69</v>
       </c>
       <c r="H10" t="n">
         <v>93.6</v>
@@ -1065,34 +1065,34 @@
         <v>1.07</v>
       </c>
       <c r="J10" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="L10" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
       <c r="M10" t="n">
         <v>1.86</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O10" t="n">
-        <v>384.62</v>
+        <v>400</v>
       </c>
       <c r="P10" t="n">
         <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="R10" t="n">
         <v>0.9</v>
       </c>
       <c r="S10" t="n">
-        <v>116.28</v>
+        <v>116.96</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1113,28 +1113,28 @@
         <v>3.8</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G11" t="n">
-        <v>54.79</v>
+        <v>52.77</v>
       </c>
       <c r="H11" t="n">
-        <v>98.2</v>
+        <v>98.1</v>
       </c>
       <c r="I11" t="n">
         <v>1.02</v>
       </c>
       <c r="J11" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="L11" t="n">
-        <v>73.3</v>
+        <v>73.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1146,13 +1146,13 @@
         <v>1.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.9</v>
+        <v>91.74</v>
       </c>
       <c r="R11" t="n">
         <v>0.5</v>
       </c>
       <c r="S11" t="n">
-        <v>194.17</v>
+        <v>198.02</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1173,28 +1173,28 @@
         <v>3.7</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>48.66</v>
+        <v>50.13</v>
       </c>
       <c r="H12" t="n">
-        <v>97.9</v>
+        <v>98</v>
       </c>
       <c r="I12" t="n">
         <v>1.02</v>
       </c>
       <c r="J12" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4.07</v>
       </c>
       <c r="L12" t="n">
-        <v>74.7</v>
+        <v>75.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="N12" t="n">
         <v>0.1</v>
@@ -1206,13 +1206,13 @@
         <v>0.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>121.95</v>
+        <v>129.87</v>
       </c>
       <c r="R12" t="n">
         <v>0.3</v>
       </c>
       <c r="S12" t="n">
-        <v>322.58</v>
+        <v>333.33</v>
       </c>
       <c r="T12"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>0.3</v>
       </c>
       <c r="G13" t="n">
-        <v>370.37</v>
+        <v>377.36</v>
       </c>
       <c r="H13" t="n">
         <v>99.7</v>
@@ -1248,7 +1248,7 @@
         <v>10.5</v>
       </c>
       <c r="K13" t="n">
-        <v>9.5</v>
+        <v>9.51</v>
       </c>
       <c r="L13" t="n">
         <v>89.5</v>
@@ -1261,16 +1261,16 @@
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>392.16</v>
+        <v>408.16</v>
       </c>
       <c r="R13" t="n">
         <v>0.1</v>
       </c>
       <c r="S13" t="n">
-        <v>869.57</v>
+        <v>952.38</v>
       </c>
       <c r="T13"/>
     </row>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -74,70 +74,70 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberraraiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldcoasttitans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Coast Titans</t>
+  </si>
+  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">goldcoasttitans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Coast Titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
     <t xml:space="preserve">sydneyroosters</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weststigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wests Tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronullasharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">canterburybulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
-    <t xml:space="preserve">weststigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wests Tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberraraiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronullasharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
   </si>
   <si>
     <t xml:space="preserve">nqcowboys</t>
@@ -564,55 +564,55 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="F2" t="n">
-        <v>72.3</v>
+        <v>92.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="H2" t="n">
-        <v>27.7</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.61</v>
+        <v>13.43</v>
       </c>
       <c r="J2" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>42.83</v>
+        <v>6666.67</v>
       </c>
       <c r="N2" t="n">
-        <v>21.2</v>
+        <v>51.5</v>
       </c>
       <c r="O2" t="n">
-        <v>4.72</v>
+        <v>1.94</v>
       </c>
       <c r="P2" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>23.7</v>
+        <v>20.4</v>
       </c>
       <c r="S2" t="n">
-        <v>4.23</v>
+        <v>4.89</v>
       </c>
       <c r="T2"/>
     </row>
@@ -624,55 +624,55 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="F3" t="n">
-        <v>74.2</v>
+        <v>43.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>25.8</v>
+        <v>56.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.88</v>
+        <v>1.77</v>
       </c>
       <c r="J3" t="n">
-        <v>97.7</v>
+        <v>95.4</v>
       </c>
       <c r="K3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
-        <v>44.25</v>
+        <v>21.86</v>
       </c>
       <c r="N3" t="n">
-        <v>22.1</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>4.53</v>
+        <v>36.56</v>
       </c>
       <c r="P3" t="n">
-        <v>38.8</v>
+        <v>32.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.57</v>
+        <v>3.06</v>
       </c>
       <c r="R3" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="S3" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="T3"/>
     </row>
@@ -687,52 +687,52 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>68.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>31.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="J4" t="n">
-        <v>98.1</v>
+        <v>99.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>52.91</v>
+        <v>129.87</v>
       </c>
       <c r="N4" t="n">
-        <v>25.9</v>
+        <v>13.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.86</v>
+        <v>7.62</v>
       </c>
       <c r="P4" t="n">
-        <v>35.7</v>
+        <v>31.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="R4" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="S4" t="n">
-        <v>6.08</v>
+        <v>6.22</v>
       </c>
       <c r="T4"/>
     </row>
@@ -744,55 +744,55 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="E5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="F5" t="n">
-        <v>78.8</v>
+        <v>54.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>21.2</v>
+        <v>45.6</v>
       </c>
       <c r="I5" t="n">
-        <v>4.71</v>
+        <v>2.19</v>
       </c>
       <c r="J5" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>76.92</v>
+        <v>44.94</v>
       </c>
       <c r="N5" t="n">
-        <v>24.6</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>4.07</v>
+        <v>14.3</v>
       </c>
       <c r="P5" t="n">
-        <v>36</v>
+        <v>29.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.77</v>
+        <v>3.36</v>
       </c>
       <c r="R5" t="n">
-        <v>16.4</v>
+        <v>15.5</v>
       </c>
       <c r="S5" t="n">
-        <v>6.11</v>
+        <v>6.45</v>
       </c>
       <c r="T5"/>
     </row>
@@ -804,55 +804,55 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="F6" t="n">
-        <v>25.7</v>
+        <v>81.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.89</v>
+        <v>1.22</v>
       </c>
       <c r="H6" t="n">
-        <v>74.3</v>
+        <v>18.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.35</v>
+        <v>5.51</v>
       </c>
       <c r="J6" t="n">
-        <v>84.4</v>
+        <v>99.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>15.6</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>6.39</v>
+        <v>833.33</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>21.5</v>
       </c>
       <c r="O6" t="n">
-        <v>79.68</v>
+        <v>4.64</v>
       </c>
       <c r="P6" t="n">
-        <v>14.5</v>
+        <v>29.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.89</v>
+        <v>3.41</v>
       </c>
       <c r="R6" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>12.94</v>
+        <v>7.98</v>
       </c>
       <c r="T6"/>
     </row>
@@ -864,55 +864,55 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="F7" t="n">
-        <v>25.9</v>
+        <v>44.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.86</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>74.1</v>
+        <v>55.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="J7" t="n">
-        <v>77.8</v>
+        <v>95.9</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="L7" t="n">
-        <v>22.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
-        <v>4.51</v>
+        <v>24.27</v>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>51.95</v>
+        <v>25.91</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>23.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.33</v>
+        <v>4.25</v>
       </c>
       <c r="R7" t="n">
-        <v>5.9</v>
+        <v>11.4</v>
       </c>
       <c r="S7" t="n">
-        <v>16.84</v>
+        <v>8.76</v>
       </c>
       <c r="T7"/>
     </row>
@@ -924,55 +924,55 @@
         <v>33</v>
       </c>
       <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>72.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="H8" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="J8" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="P8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.36</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="S8" t="n">
-        <v>18.47</v>
+        <v>50.38</v>
       </c>
       <c r="T8"/>
     </row>
@@ -987,52 +987,52 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F9" t="n">
-        <v>9.2</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>10.83</v>
+        <v>34.42</v>
       </c>
       <c r="H9" t="n">
-        <v>90.8</v>
+        <v>97.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="J9" t="n">
-        <v>56.7</v>
+        <v>55.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="L9" t="n">
-        <v>43.3</v>
+        <v>44.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>246.91</v>
+        <v>10000</v>
       </c>
       <c r="P9" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.63</v>
+        <v>28.01</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>41.67</v>
+        <v>65.79</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1047,52 +1047,50 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>15.69</v>
+        <v>138.89</v>
       </c>
       <c r="H10" t="n">
-        <v>93.6</v>
+        <v>99.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="J10" t="n">
-        <v>46.2</v>
+        <v>31.4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="L10" t="n">
-        <v>53.8</v>
+        <v>68.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O10"/>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.1</v>
+        <v>106.95</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="S10" t="n">
-        <v>116.96</v>
+        <v>350.88</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1107,52 +1105,50 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="G11" t="n">
-        <v>52.77</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>98.1</v>
+        <v>99.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>26.9</v>
+        <v>22.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.72</v>
+        <v>4.52</v>
       </c>
       <c r="L11" t="n">
-        <v>73.1</v>
+        <v>77.9</v>
       </c>
       <c r="M11" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="n">
-        <v>5000</v>
-      </c>
+      <c r="O11"/>
       <c r="P11" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>91.74</v>
+        <v>161.29</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="S11" t="n">
-        <v>198.02</v>
+        <v>425.53</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1167,52 +1163,50 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="G12" t="n">
-        <v>50.13</v>
+        <v>277.78</v>
       </c>
       <c r="H12" t="n">
-        <v>98</v>
+        <v>99.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>24.6</v>
+        <v>16.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.07</v>
+        <v>5.93</v>
       </c>
       <c r="L12" t="n">
-        <v>75.4</v>
+        <v>83.1</v>
       </c>
       <c r="M12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12"/>
+      <c r="P12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>224.72</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O12" t="n">
-        <v>1818.18</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>129.87</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3</v>
-      </c>
       <c r="S12" t="n">
-        <v>333.33</v>
+        <v>714.29</v>
       </c>
       <c r="T12"/>
     </row>
@@ -1224,47 +1218,47 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>3.3</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G13" t="n">
-        <v>377.36</v>
+        <v>454.55</v>
       </c>
       <c r="H13" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>10.5</v>
+        <v>13.7</v>
       </c>
       <c r="K13" t="n">
-        <v>9.51</v>
+        <v>7.32</v>
       </c>
       <c r="L13" t="n">
-        <v>89.5</v>
+        <v>86.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>408.16</v>
+        <v>333.33</v>
       </c>
       <c r="R13" t="n">
         <v>0.1</v>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -74,18 +74,18 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">canberraraiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbanebroncos</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
-    <t xml:space="preserve">canberraraiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
     <t xml:space="preserve">goldcoasttitans</t>
   </si>
   <si>
@@ -98,18 +98,18 @@
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydneyroosters</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
     <t xml:space="preserve">weststigers</t>
   </si>
   <si>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
   </si>
   <si>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
+  </si>
+  <si>
     <t xml:space="preserve">canterburybulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
@@ -564,55 +564,55 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4</v>
+        <v>6.3</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="F2" t="n">
-        <v>92.6</v>
+        <v>50.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.08</v>
+        <v>1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>49.2</v>
       </c>
       <c r="I2" t="n">
-        <v>13.43</v>
+        <v>2.03</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>6666.67</v>
+        <v>30.3</v>
       </c>
       <c r="N2" t="n">
-        <v>51.5</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.94</v>
+        <v>22.52</v>
       </c>
       <c r="P2" t="n">
-        <v>42</v>
+        <v>39.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="R2" t="n">
-        <v>20.4</v>
+        <v>24.6</v>
       </c>
       <c r="S2" t="n">
-        <v>4.89</v>
+        <v>4.07</v>
       </c>
       <c r="T2"/>
     </row>
@@ -624,55 +624,55 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1</v>
+        <v>8.2</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1</v>
+        <v>8.2</v>
       </c>
       <c r="F3" t="n">
-        <v>43.5</v>
+        <v>90.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="H3" t="n">
-        <v>56.5</v>
+        <v>9.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.77</v>
+        <v>10.24</v>
       </c>
       <c r="J3" t="n">
-        <v>95.4</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>21.86</v>
+        <v>2857.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>47.6</v>
       </c>
       <c r="O3" t="n">
-        <v>36.56</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>32.7</v>
+        <v>37.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.06</v>
+        <v>2.64</v>
       </c>
       <c r="R3" t="n">
-        <v>19.8</v>
+        <v>17.7</v>
       </c>
       <c r="S3" t="n">
-        <v>5.06</v>
+        <v>5.65</v>
       </c>
       <c r="T3"/>
     </row>
@@ -687,52 +687,52 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="E4" t="n">
         <v>7.1</v>
       </c>
       <c r="F4" t="n">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>31.7</v>
+        <v>32.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>99.2</v>
+        <v>99.1</v>
       </c>
       <c r="K4" t="n">
         <v>1.01</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>129.87</v>
+        <v>112.99</v>
       </c>
       <c r="N4" t="n">
-        <v>13.1</v>
+        <v>14.8</v>
       </c>
       <c r="O4" t="n">
-        <v>7.62</v>
+        <v>6.78</v>
       </c>
       <c r="P4" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
       <c r="S4" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="T4"/>
     </row>
@@ -747,52 +747,52 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="E5" t="n">
         <v>6.6</v>
       </c>
       <c r="F5" t="n">
-        <v>54.4</v>
+        <v>52.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
-        <v>45.6</v>
+        <v>47.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="J5" t="n">
-        <v>97.8</v>
+        <v>97.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>44.94</v>
+        <v>36.17</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O5" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="P5" t="n">
-        <v>29.8</v>
+        <v>28.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="R5" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="S5" t="n">
-        <v>6.45</v>
+        <v>6.82</v>
       </c>
       <c r="T5"/>
     </row>
@@ -804,55 +804,55 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="E6" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="F6" t="n">
-        <v>81.9</v>
+        <v>47.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.22</v>
+        <v>2.13</v>
       </c>
       <c r="H6" t="n">
-        <v>18.1</v>
+        <v>52.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.51</v>
+        <v>1.89</v>
       </c>
       <c r="J6" t="n">
-        <v>99.9</v>
+        <v>95.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>833.33</v>
+        <v>24.39</v>
       </c>
       <c r="N6" t="n">
-        <v>21.5</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.64</v>
+        <v>18.69</v>
       </c>
       <c r="P6" t="n">
-        <v>29.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.41</v>
+        <v>3.91</v>
       </c>
       <c r="R6" t="n">
         <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>7.98</v>
+        <v>7.99</v>
       </c>
       <c r="T6"/>
     </row>
@@ -864,55 +864,55 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="F7" t="n">
-        <v>44.6</v>
+        <v>77.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>1.29</v>
       </c>
       <c r="H7" t="n">
-        <v>55.4</v>
+        <v>22.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.81</v>
+        <v>4.45</v>
       </c>
       <c r="J7" t="n">
-        <v>95.9</v>
+        <v>99.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>24.27</v>
+        <v>512.82</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>19.9</v>
       </c>
       <c r="O7" t="n">
-        <v>25.91</v>
+        <v>5.02</v>
       </c>
       <c r="P7" t="n">
-        <v>23.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="S7" t="n">
-        <v>8.76</v>
+        <v>9.82</v>
       </c>
       <c r="T7"/>
     </row>
@@ -927,52 +927,52 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E8" t="n">
         <v>5.3</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>9.8</v>
       </c>
       <c r="G8" t="n">
-        <v>9.59</v>
+        <v>10.2</v>
       </c>
       <c r="H8" t="n">
-        <v>89.6</v>
+        <v>90.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="J8" t="n">
-        <v>72.1</v>
+        <v>69.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="L8" t="n">
-        <v>27.9</v>
+        <v>30.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
         <v>0.3</v>
       </c>
       <c r="O8" t="n">
-        <v>370.37</v>
+        <v>333.33</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.2</v>
+        <v>19.51</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="T8"/>
     </row>
@@ -993,28 +993,28 @@
         <v>4.3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>34.42</v>
+        <v>30.44</v>
       </c>
       <c r="H9" t="n">
-        <v>97.1</v>
+        <v>96.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.03</v>
       </c>
       <c r="J9" t="n">
-        <v>55.7</v>
+        <v>55.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1023,16 +1023,16 @@
         <v>10000</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.01</v>
+        <v>24.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
-        <v>65.79</v>
+        <v>57.47</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1044,53 +1044,53 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G10" t="n">
-        <v>138.89</v>
+        <v>476.19</v>
       </c>
       <c r="H10" t="n">
-        <v>99.3</v>
+        <v>99.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>31.4</v>
+        <v>26.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.19</v>
+        <v>3.74</v>
       </c>
       <c r="L10" t="n">
-        <v>68.6</v>
+        <v>73.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>106.95</v>
+        <v>102.04</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="S10" t="n">
-        <v>350.88</v>
+        <v>243.9</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1102,53 +1102,53 @@
         <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>137.93</v>
       </c>
       <c r="H11" t="n">
-        <v>99.9</v>
+        <v>99.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J11" t="n">
-        <v>22.1</v>
+        <v>30.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.52</v>
+        <v>3.32</v>
       </c>
       <c r="L11" t="n">
-        <v>77.9</v>
+        <v>69.9</v>
       </c>
       <c r="M11" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>161.29</v>
+        <v>102.56</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="S11" t="n">
-        <v>425.53</v>
+        <v>322.58</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1163,7 +1163,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E12" t="n">
         <v>3.5</v>
@@ -1172,7 +1172,7 @@
         <v>0.4</v>
       </c>
       <c r="G12" t="n">
-        <v>277.78</v>
+        <v>270.27</v>
       </c>
       <c r="H12" t="n">
         <v>99.6</v>
@@ -1181,32 +1181,32 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="L12" t="n">
-        <v>83.1</v>
+        <v>83</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>224.72</v>
+        <v>202.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="S12" t="n">
-        <v>714.29</v>
+        <v>625</v>
       </c>
       <c r="T12"/>
     </row>
@@ -1230,7 +1230,7 @@
         <v>0.2</v>
       </c>
       <c r="G13" t="n">
-        <v>454.55</v>
+        <v>487.8</v>
       </c>
       <c r="H13" t="n">
         <v>99.8</v>
@@ -1239,16 +1239,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>13.7</v>
+        <v>12.6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.32</v>
+        <v>7.96</v>
       </c>
       <c r="L13" t="n">
-        <v>86.3</v>
+        <v>87.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>0.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>333.33</v>
+        <v>363.64</v>
       </c>
       <c r="R13" t="n">
         <v>0.1</v>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -74,16 +74,28 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">sydneyroosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
     <t xml:space="preserve">canberraraiders</t>
   </si>
   <si>
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
+    <t xml:space="preserve">weststigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wests Tigers</t>
   </si>
   <si>
     <t xml:space="preserve">goldcoasttitans</t>
@@ -92,58 +104,46 @@
     <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydneyroosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weststigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wests Tigers</t>
+    <t xml:space="preserve">stgeorgeillawarradragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St George-Illawarra Dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterburybulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nqcowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Queensland Cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
     <t xml:space="preserve">cronullasharks</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterburybulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stgeorgeillawarradragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nqcowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Queensland Cowboys</t>
   </si>
 </sst>
 </file>
@@ -564,55 +564,53 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3</v>
+        <v>9.4</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="F2" t="n">
-        <v>50.8</v>
+        <v>99.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.97</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>49.2</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.03</v>
+        <v>500</v>
       </c>
       <c r="J2" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M2" t="n">
-        <v>30.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M2"/>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>84.7</v>
       </c>
       <c r="O2" t="n">
-        <v>22.52</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>39.2</v>
+        <v>68.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>24.6</v>
+        <v>41.8</v>
       </c>
       <c r="S2" t="n">
-        <v>4.07</v>
+        <v>2.4</v>
       </c>
       <c r="T2"/>
     </row>
@@ -627,22 +625,22 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.2</v>
+        <v>7.8</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2</v>
+        <v>7.8</v>
       </c>
       <c r="F3" t="n">
-        <v>90.2</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="H3" t="n">
-        <v>9.8</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>10.24</v>
+        <v>7.15</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -657,22 +655,22 @@
         <v>2857.14</v>
       </c>
       <c r="N3" t="n">
-        <v>47.6</v>
+        <v>11.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>8.72</v>
       </c>
       <c r="P3" t="n">
-        <v>37.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="S3" t="n">
-        <v>5.65</v>
+        <v>5.54</v>
       </c>
       <c r="T3"/>
     </row>
@@ -684,55 +682,55 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>67.7</v>
+        <v>40.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>2.47</v>
       </c>
       <c r="H4" t="n">
-        <v>32.3</v>
+        <v>59.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>99.1</v>
+        <v>97</v>
       </c>
       <c r="K4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>112.99</v>
+        <v>33.78</v>
       </c>
       <c r="N4" t="n">
-        <v>14.8</v>
+        <v>0.4</v>
       </c>
       <c r="O4" t="n">
-        <v>6.78</v>
+        <v>256.41</v>
       </c>
       <c r="P4" t="n">
-        <v>31.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>4.31</v>
       </c>
       <c r="R4" t="n">
-        <v>15.6</v>
+        <v>12.4</v>
       </c>
       <c r="S4" t="n">
-        <v>6.4</v>
+        <v>8.07</v>
       </c>
       <c r="T4"/>
     </row>
@@ -744,55 +742,55 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>52.1</v>
+        <v>53.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>47.9</v>
+        <v>46.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="J5" t="n">
-        <v>97.2</v>
+        <v>98.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>36.17</v>
+        <v>79.05</v>
       </c>
       <c r="N5" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>13.1</v>
+        <v>110.5</v>
       </c>
       <c r="P5" t="n">
-        <v>28.8</v>
+        <v>20.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.48</v>
+        <v>4.82</v>
       </c>
       <c r="R5" t="n">
-        <v>14.7</v>
+        <v>9.2</v>
       </c>
       <c r="S5" t="n">
-        <v>6.82</v>
+        <v>10.89</v>
       </c>
       <c r="T5"/>
     </row>
@@ -804,55 +802,55 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="F6" t="n">
-        <v>47.1</v>
+        <v>59.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.13</v>
+        <v>1.69</v>
       </c>
       <c r="H6" t="n">
-        <v>52.9</v>
+        <v>40.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="J6" t="n">
-        <v>95.9</v>
+        <v>99.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>24.39</v>
+        <v>952.38</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>18.69</v>
+        <v>56.66</v>
       </c>
       <c r="P6" t="n">
-        <v>25.6</v>
+        <v>19.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.91</v>
+        <v>5.1</v>
       </c>
       <c r="R6" t="n">
-        <v>12.5</v>
+        <v>7.3</v>
       </c>
       <c r="S6" t="n">
-        <v>7.99</v>
+        <v>13.71</v>
       </c>
       <c r="T6"/>
     </row>
@@ -864,55 +862,55 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="E7" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="F7" t="n">
-        <v>77.5</v>
+        <v>32.1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29</v>
+        <v>3.11</v>
       </c>
       <c r="H7" t="n">
-        <v>22.5</v>
+        <v>67.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4.45</v>
+        <v>1.47</v>
       </c>
       <c r="J7" t="n">
-        <v>99.8</v>
+        <v>95.9</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.2</v>
       </c>
-      <c r="M7" t="n">
-        <v>512.82</v>
-      </c>
-      <c r="N7" t="n">
-        <v>19.9</v>
-      </c>
       <c r="O7" t="n">
-        <v>5.02</v>
+        <v>500</v>
       </c>
       <c r="P7" t="n">
-        <v>25.5</v>
+        <v>13.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>7.46</v>
       </c>
       <c r="R7" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>9.82</v>
+        <v>16.69</v>
       </c>
       <c r="T7"/>
     </row>
@@ -924,55 +922,55 @@
         <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="F8" t="n">
-        <v>9.8</v>
+        <v>28.6</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>90.2</v>
+        <v>71.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>69.3</v>
+        <v>97.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="L8" t="n">
-        <v>30.7</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.26</v>
+        <v>36.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>333.33</v>
+        <v>183.49</v>
       </c>
       <c r="P8" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.51</v>
+        <v>8.33</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="S8" t="n">
-        <v>50.13</v>
+        <v>20.49</v>
       </c>
       <c r="T8"/>
     </row>
@@ -987,52 +985,50 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>30.44</v>
+        <v>952.38</v>
       </c>
       <c r="H9" t="n">
-        <v>96.7</v>
+        <v>99.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>55.5</v>
+        <v>43.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>56.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="O9"/>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.88</v>
+        <v>151.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="S9" t="n">
-        <v>57.47</v>
+        <v>370.37</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1044,53 +1040,53 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>476.19</v>
+        <v>217.39</v>
       </c>
       <c r="H10" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>26.7</v>
+        <v>34.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="L10" t="n">
-        <v>73.3</v>
+        <v>65.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>102.04</v>
+        <v>333.33</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="S10" t="n">
-        <v>243.9</v>
+        <v>800</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1102,53 +1098,51 @@
         <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>137.93</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11"/>
       <c r="H11" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>30.1</v>
+        <v>7.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.32</v>
+        <v>13.05</v>
       </c>
       <c r="L11" t="n">
-        <v>69.9</v>
+        <v>92.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>102.56</v>
+        <v>2857.14</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>322.58</v>
+        <v>10000</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1160,53 +1154,51 @@
         <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>270.27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G12"/>
       <c r="H12" t="n">
-        <v>99.6</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.87</v>
+        <v>10.43</v>
       </c>
       <c r="L12" t="n">
-        <v>83</v>
+        <v>90.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>202.02</v>
+        <v>3333.33</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>625</v>
+        <v>4000</v>
       </c>
       <c r="T12"/>
     </row>
@@ -1221,50 +1213,50 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>487.8</v>
+        <v>4000</v>
       </c>
       <c r="H13" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>12.6</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>7.96</v>
+        <v>6.27</v>
       </c>
       <c r="L13" t="n">
-        <v>87.4</v>
+        <v>84</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>363.64</v>
+        <v>1818.18</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>952.38</v>
+        <v>6666.67</v>
       </c>
       <c r="T13"/>
     </row>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -116,34 +116,34 @@
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
+    <t xml:space="preserve">canterburybulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
   </si>
   <si>
-    <t xml:space="preserve">canterburybulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
-  </si>
-  <si>
     <t xml:space="preserve">nqcowboys</t>
   </si>
   <si>
     <t xml:space="preserve">North Queensland Cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">cronullasharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">parramattaeels</t>
   </si>
   <si>
     <t xml:space="preserve">Parramatta Eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronullasharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
   </si>
 </sst>
 </file>
@@ -567,22 +567,22 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4</v>
+        <v>9.8</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4</v>
+        <v>9.7</v>
       </c>
       <c r="F2" t="n">
-        <v>99.8</v>
+        <v>99.9</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>500</v>
+        <v>1428.57</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -595,22 +595,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>84.7</v>
+        <v>86</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>68.6</v>
+        <v>69</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R2" t="n">
-        <v>41.8</v>
+        <v>42.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="T2"/>
     </row>
@@ -625,22 +625,22 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>93.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="I3" t="n">
-        <v>7.15</v>
+        <v>15.28</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -652,25 +652,25 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2857.14</v>
+        <v>4000</v>
       </c>
       <c r="N3" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="O3" t="n">
-        <v>8.72</v>
+        <v>8.14</v>
       </c>
       <c r="P3" t="n">
-        <v>41.4</v>
+        <v>50.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
-        <v>18.1</v>
+        <v>23.8</v>
       </c>
       <c r="S3" t="n">
-        <v>5.54</v>
+        <v>4.21</v>
       </c>
       <c r="T3"/>
     </row>
@@ -685,52 +685,52 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="F4" t="n">
-        <v>40.5</v>
+        <v>49.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.47</v>
+        <v>2.03</v>
       </c>
       <c r="H4" t="n">
-        <v>59.5</v>
+        <v>50.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="J4" t="n">
-        <v>97</v>
+        <v>98.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>33.78</v>
+        <v>56.66</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>256.41</v>
+        <v>487.8</v>
       </c>
       <c r="P4" t="n">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.31</v>
+        <v>4.03</v>
       </c>
       <c r="R4" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S4" t="n">
-        <v>8.07</v>
+        <v>8.19</v>
       </c>
       <c r="T4"/>
     </row>
@@ -751,16 +751,16 @@
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>53.2</v>
+        <v>52.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>46.8</v>
+        <v>47.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J5" t="n">
         <v>98.7</v>
@@ -772,25 +772,25 @@
         <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>79.05</v>
+        <v>75.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="O5" t="n">
-        <v>110.5</v>
+        <v>253.16</v>
       </c>
       <c r="P5" t="n">
-        <v>20.8</v>
+        <v>18.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.82</v>
+        <v>5.28</v>
       </c>
       <c r="R5" t="n">
-        <v>9.2</v>
+        <v>7.9</v>
       </c>
       <c r="S5" t="n">
-        <v>10.89</v>
+        <v>12.71</v>
       </c>
       <c r="T5"/>
     </row>
@@ -811,46 +811,46 @@
         <v>6.9</v>
       </c>
       <c r="F6" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="J6" t="n">
-        <v>99.9</v>
+        <v>99.8</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>952.38</v>
+        <v>555.56</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>56.66</v>
+        <v>102.56</v>
       </c>
       <c r="P6" t="n">
-        <v>19.6</v>
+        <v>17.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.1</v>
+        <v>5.74</v>
       </c>
       <c r="R6" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="S6" t="n">
-        <v>13.71</v>
+        <v>15.92</v>
       </c>
       <c r="T6"/>
     </row>
@@ -865,52 +865,52 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="F7" t="n">
-        <v>32.1</v>
+        <v>23.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.11</v>
+        <v>4.23</v>
       </c>
       <c r="H7" t="n">
-        <v>67.9</v>
+        <v>76.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="J7" t="n">
-        <v>95.9</v>
+        <v>93.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="L7" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>24.54</v>
+        <v>14.45</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="P7" t="n">
-        <v>13.4</v>
+        <v>9.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.46</v>
+        <v>10.12</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>16.69</v>
+        <v>24.72</v>
       </c>
       <c r="T7"/>
     </row>
@@ -925,52 +925,52 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="F8" t="n">
-        <v>28.6</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="H8" t="n">
-        <v>71.4</v>
+        <v>81</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="J8" t="n">
-        <v>97.3</v>
+        <v>95.1</v>
       </c>
       <c r="K8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="L8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>869.57</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="R8" t="n">
         <v>2.7</v>
       </c>
-      <c r="M8" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>183.49</v>
-      </c>
-      <c r="P8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="S8" t="n">
-        <v>20.49</v>
+        <v>37.24</v>
       </c>
       <c r="T8"/>
     </row>
@@ -982,53 +982,53 @@
         <v>35</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>952.38</v>
+        <v>42.64</v>
       </c>
       <c r="H9" t="n">
-        <v>99.9</v>
+        <v>97.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="J9" t="n">
-        <v>43.7</v>
+        <v>55.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.29</v>
+        <v>1.81</v>
       </c>
       <c r="L9" t="n">
-        <v>56.3</v>
+        <v>44.9</v>
       </c>
       <c r="M9" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>151.52</v>
+        <v>94.79</v>
       </c>
       <c r="R9" t="n">
         <v>0.3</v>
       </c>
       <c r="S9" t="n">
-        <v>370.37</v>
+        <v>350.88</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1040,53 +1040,53 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>217.39</v>
+        <v>2500</v>
       </c>
       <c r="H10" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>34.3</v>
+        <v>32.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>65.7</v>
+        <v>67.8</v>
       </c>
       <c r="M10" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>333.33</v>
+        <v>222.22</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="S10" t="n">
-        <v>800</v>
+        <v>512.82</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1101,15 +1101,17 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11"/>
+      <c r="G11" t="n">
+        <v>20000</v>
+      </c>
       <c r="H11" t="n">
         <v>100</v>
       </c>
@@ -1117,32 +1119,32 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>7.7</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>13.05</v>
+        <v>8.33</v>
       </c>
       <c r="L11" t="n">
-        <v>92.3</v>
+        <v>88</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2857.14</v>
+        <v>1052.63</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1154,7 +1156,7 @@
         <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>2.9</v>
@@ -1165,7 +1167,9 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12"/>
+      <c r="G12" t="n">
+        <v>6666.67</v>
+      </c>
       <c r="H12" t="n">
         <v>100</v>
       </c>
@@ -1173,16 +1177,16 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>9.6</v>
+        <v>14.1</v>
       </c>
       <c r="K12" t="n">
-        <v>10.43</v>
+        <v>7.1</v>
       </c>
       <c r="L12" t="n">
-        <v>90.4</v>
+        <v>85.9</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1192,13 +1196,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3333.33</v>
+        <v>2000</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="T12"/>
     </row>
@@ -1210,20 +1214,18 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
-        <v>4000</v>
-      </c>
+      <c r="G13"/>
       <c r="H13" t="n">
         <v>100</v>
       </c>
@@ -1231,33 +1233,29 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>1.7</v>
       </c>
       <c r="K13" t="n">
-        <v>6.27</v>
+        <v>59.7</v>
       </c>
       <c r="L13" t="n">
-        <v>84</v>
+        <v>98.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1818.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q13"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
-        <v>6666.67</v>
-      </c>
+      <c r="S13"/>
       <c r="T13"/>
     </row>
   </sheetData>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -567,10 +567,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8</v>
+        <v>9.6</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7</v>
+        <v>9.5</v>
       </c>
       <c r="F2" t="n">
         <v>99.9</v>
@@ -582,7 +582,7 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1428.57</v>
+        <v>714.29</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -595,22 +595,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>42.6</v>
+        <v>38.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="T2"/>
     </row>
@@ -625,22 +625,22 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1</v>
+        <v>8.3</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>8.3</v>
       </c>
       <c r="F3" t="n">
-        <v>93.5</v>
+        <v>95.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>15.28</v>
+        <v>23.98</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -652,25 +652,25 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4000</v>
+        <v>6666.67</v>
       </c>
       <c r="N3" t="n">
-        <v>12.3</v>
+        <v>19.9</v>
       </c>
       <c r="O3" t="n">
-        <v>8.14</v>
+        <v>5.04</v>
       </c>
       <c r="P3" t="n">
-        <v>50.7</v>
+        <v>57.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>23.8</v>
+        <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>4.21</v>
+        <v>3.33</v>
       </c>
       <c r="T3"/>
     </row>
@@ -685,52 +685,52 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="F4" t="n">
-        <v>49.2</v>
+        <v>42.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="H4" t="n">
-        <v>50.8</v>
+        <v>57.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="J4" t="n">
-        <v>98.2</v>
+        <v>97.6</v>
       </c>
       <c r="K4" t="n">
         <v>1.02</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>56.66</v>
+        <v>41.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O4" t="n">
-        <v>487.8</v>
+        <v>714.29</v>
       </c>
       <c r="P4" t="n">
-        <v>24.8</v>
+        <v>20.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.03</v>
+        <v>4.96</v>
       </c>
       <c r="R4" t="n">
-        <v>12.2</v>
+        <v>9.8</v>
       </c>
       <c r="S4" t="n">
-        <v>8.19</v>
+        <v>10.24</v>
       </c>
       <c r="T4"/>
     </row>
@@ -745,52 +745,52 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F5" t="n">
-        <v>52.8</v>
+        <v>57.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="H5" t="n">
-        <v>47.2</v>
+        <v>42.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
-        <v>98.7</v>
+        <v>99.1</v>
       </c>
       <c r="K5" t="n">
         <v>1.01</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>75.47</v>
+        <v>105.26</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>253.16</v>
+        <v>181.82</v>
       </c>
       <c r="P5" t="n">
-        <v>18.9</v>
+        <v>20.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.28</v>
+        <v>4.96</v>
       </c>
       <c r="R5" t="n">
-        <v>7.9</v>
+        <v>8.7</v>
       </c>
       <c r="S5" t="n">
-        <v>12.71</v>
+        <v>11.47</v>
       </c>
       <c r="T5"/>
     </row>
@@ -805,22 +805,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="n">
-        <v>59.5</v>
+        <v>56.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="H6" t="n">
-        <v>40.5</v>
+        <v>43.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="J6" t="n">
         <v>99.8</v>
@@ -832,25 +832,25 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>555.56</v>
+        <v>487.8</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>102.56</v>
+        <v>95.24</v>
       </c>
       <c r="P6" t="n">
-        <v>17.4</v>
+        <v>15.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.74</v>
+        <v>6.59</v>
       </c>
       <c r="R6" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="S6" t="n">
-        <v>15.92</v>
+        <v>18.37</v>
       </c>
       <c r="T6"/>
     </row>
@@ -865,52 +865,52 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="F7" t="n">
-        <v>23.7</v>
+        <v>29.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.23</v>
+        <v>3.41</v>
       </c>
       <c r="H7" t="n">
-        <v>76.3</v>
+        <v>70.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="J7" t="n">
-        <v>93.1</v>
+        <v>94.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="M7" t="n">
-        <v>14.45</v>
+        <v>18.37</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5000</v>
+        <v>2222.22</v>
       </c>
       <c r="P7" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.12</v>
+        <v>8.95</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="S7" t="n">
-        <v>24.72</v>
+        <v>21.05</v>
       </c>
       <c r="T7"/>
     </row>
@@ -925,52 +925,52 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>16.1</v>
       </c>
       <c r="G8" t="n">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>81</v>
+        <v>83.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="J8" t="n">
-        <v>95.1</v>
+        <v>94.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="L8" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="M8" t="n">
-        <v>20.37</v>
+        <v>17.44</v>
       </c>
       <c r="N8" t="n">
         <v>0.1</v>
       </c>
       <c r="O8" t="n">
-        <v>869.57</v>
+        <v>800</v>
       </c>
       <c r="P8" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.05</v>
+        <v>15.64</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>37.24</v>
+        <v>47.39</v>
       </c>
       <c r="T8"/>
     </row>
@@ -985,7 +985,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="E9" t="n">
         <v>4.7</v>
@@ -994,7 +994,7 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>42.64</v>
+        <v>44.35</v>
       </c>
       <c r="H9" t="n">
         <v>97.7</v>
@@ -1003,32 +1003,32 @@
         <v>1.02</v>
       </c>
       <c r="J9" t="n">
-        <v>55.1</v>
+        <v>53.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="L9" t="n">
-        <v>44.9</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.79</v>
+        <v>105.82</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="S9" t="n">
-        <v>350.88</v>
+        <v>434.78</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1049,25 +1049,25 @@
         <v>3.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2500</v>
+        <v>1666.67</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>99.9</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="L10" t="n">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.48</v>
@@ -1080,13 +1080,13 @@
         <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>222.22</v>
+        <v>227.27</v>
       </c>
       <c r="R10" t="n">
         <v>0.2</v>
       </c>
       <c r="S10" t="n">
-        <v>512.82</v>
+        <v>500</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1119,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="K11" t="n">
-        <v>8.33</v>
+        <v>8.42</v>
       </c>
       <c r="L11" t="n">
-        <v>88</v>
+        <v>88.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>0.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1052.63</v>
+        <v>1250</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>2857.14</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6666.67</v>
+        <v>4000</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1177,26 +1177,26 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
       <c r="K12" t="n">
-        <v>7.1</v>
+        <v>6.56</v>
       </c>
       <c r="L12" t="n">
-        <v>85.9</v>
+        <v>84.8</v>
       </c>
       <c r="M12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2000</v>
+        <v>1666.67</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>1.8</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>59.7</v>
+        <v>65.15</v>
       </c>
       <c r="L13" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -74,76 +74,76 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">goldcoasttitans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Coast Titans</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydneyroosters</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warriors</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbanebroncos</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
+    <t xml:space="preserve">weststigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wests Tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">canberraraiders</t>
   </si>
   <si>
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">weststigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wests Tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldcoasttitans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Coast Titans</t>
-  </si>
-  <si>
     <t xml:space="preserve">newcastleknights</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warriors</t>
-  </si>
-  <si>
     <t xml:space="preserve">canterburybulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
+    <t xml:space="preserve">nqcowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Queensland Cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronullasharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nqcowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Queensland Cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronullasharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
   </si>
 </sst>
 </file>
@@ -567,22 +567,22 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6</v>
+        <v>8.7</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="F2" t="n">
-        <v>99.9</v>
+        <v>96.4</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>714.29</v>
+        <v>28.13</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -595,22 +595,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>78.2</v>
+        <v>24.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>4.06</v>
       </c>
       <c r="P2" t="n">
-        <v>67.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>38.7</v>
+        <v>31.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>3.18</v>
       </c>
       <c r="T2"/>
     </row>
@@ -622,25 +622,25 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="F3" t="n">
-        <v>95.8</v>
+        <v>99.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>23.98</v>
+        <v>689.66</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -651,26 +651,24 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>6666.67</v>
-      </c>
+      <c r="M3"/>
       <c r="N3" t="n">
-        <v>19.9</v>
+        <v>71.4</v>
       </c>
       <c r="O3" t="n">
-        <v>5.04</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>57.7</v>
+        <v>55.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="S3" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="T3"/>
     </row>
@@ -682,55 +680,55 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="F4" t="n">
-        <v>42.6</v>
+        <v>55.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>57.4</v>
+        <v>44.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="J4" t="n">
-        <v>97.6</v>
+        <v>99.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>41.07</v>
+        <v>555.56</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="O4" t="n">
-        <v>714.29</v>
+        <v>227.27</v>
       </c>
       <c r="P4" t="n">
-        <v>20.1</v>
+        <v>29</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.96</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>9.8</v>
+        <v>16</v>
       </c>
       <c r="S4" t="n">
-        <v>10.24</v>
+        <v>6.26</v>
       </c>
       <c r="T4"/>
     </row>
@@ -742,55 +740,53 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>57.7</v>
+        <v>67.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="H5" t="n">
-        <v>42.3</v>
+        <v>32.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>3.09</v>
       </c>
       <c r="J5" t="n">
-        <v>99.1</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>105.26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M5"/>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>181.82</v>
+        <v>43.48</v>
       </c>
       <c r="P5" t="n">
-        <v>20.2</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.96</v>
+        <v>4.16</v>
       </c>
       <c r="R5" t="n">
-        <v>8.7</v>
+        <v>11</v>
       </c>
       <c r="S5" t="n">
-        <v>11.47</v>
+        <v>9.06</v>
       </c>
       <c r="T5"/>
     </row>
@@ -805,22 +801,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="F6" t="n">
-        <v>56.3</v>
+        <v>60.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="n">
-        <v>43.7</v>
+        <v>39.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="J6" t="n">
         <v>99.8</v>
@@ -832,25 +828,25 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>487.8</v>
+        <v>555.56</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>95.24</v>
+        <v>86.96</v>
       </c>
       <c r="P6" t="n">
-        <v>15.2</v>
+        <v>20.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.59</v>
+        <v>4.84</v>
       </c>
       <c r="R6" t="n">
-        <v>5.4</v>
+        <v>9.3</v>
       </c>
       <c r="S6" t="n">
-        <v>18.37</v>
+        <v>10.76</v>
       </c>
       <c r="T6"/>
     </row>
@@ -862,55 +858,55 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="F7" t="n">
-        <v>29.3</v>
+        <v>14.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.41</v>
+        <v>7.02</v>
       </c>
       <c r="H7" t="n">
-        <v>70.7</v>
+        <v>85.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="J7" t="n">
-        <v>94.6</v>
+        <v>97.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="L7" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>18.37</v>
+        <v>42.19</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2222.22</v>
+        <v>2857.14</v>
       </c>
       <c r="P7" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.95</v>
+        <v>11.85</v>
       </c>
       <c r="R7" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
-        <v>21.05</v>
+        <v>31.75</v>
       </c>
       <c r="T7"/>
     </row>
@@ -922,55 +918,53 @@
         <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="E8" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="F8" t="n">
-        <v>16.1</v>
+        <v>3.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>26.14</v>
       </c>
       <c r="H8" t="n">
-        <v>83.9</v>
+        <v>96.2</v>
       </c>
       <c r="I8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J8" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="K8" t="n">
         <v>1.19</v>
       </c>
-      <c r="J8" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="L8" t="n">
-        <v>5.7</v>
+        <v>16.3</v>
       </c>
       <c r="M8" t="n">
-        <v>17.44</v>
+        <v>6.14</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O8"/>
       <c r="P8" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.64</v>
+        <v>26.39</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>47.39</v>
+        <v>74.63</v>
       </c>
       <c r="T8"/>
     </row>
@@ -985,50 +979,50 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>44.35</v>
+        <v>49.14</v>
       </c>
       <c r="H9" t="n">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="I9" t="n">
         <v>1.02</v>
       </c>
       <c r="J9" t="n">
-        <v>53.7</v>
+        <v>79.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="L9" t="n">
-        <v>46.3</v>
+        <v>20.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.16</v>
+        <v>4.88</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>105.82</v>
+        <v>33.11</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="S9" t="n">
-        <v>434.78</v>
+        <v>91.74</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1040,53 +1034,51 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1666.67</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10"/>
       <c r="H10" t="n">
-        <v>99.9</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>32.5</v>
+        <v>20.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.08</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>67.5</v>
+        <v>79.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>227.27</v>
+        <v>1052.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>500</v>
+        <v>6666.67</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1101,17 +1093,15 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
-        <v>20000</v>
-      </c>
+      <c r="G11"/>
       <c r="H11" t="n">
         <v>100</v>
       </c>
@@ -1119,32 +1109,32 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="K11" t="n">
-        <v>8.42</v>
+        <v>13.47</v>
       </c>
       <c r="L11" t="n">
-        <v>88.1</v>
+        <v>92.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1250</v>
+        <v>5000</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2857.14</v>
+        <v>20000</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1159,17 +1149,15 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
-        <v>4000</v>
-      </c>
+      <c r="G12"/>
       <c r="H12" t="n">
         <v>100</v>
       </c>
@@ -1177,33 +1165,31 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>15.2</v>
+        <v>7.1</v>
       </c>
       <c r="K12" t="n">
-        <v>6.56</v>
+        <v>14.03</v>
       </c>
       <c r="L12" t="n">
-        <v>84.8</v>
+        <v>92.9</v>
       </c>
       <c r="M12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1666.67</v>
+        <v>6666.67</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="S12"/>
       <c r="T12"/>
     </row>
     <row r="13">
@@ -1214,13 +1200,13 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1233,16 +1219,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>65.15</v>
+        <v>24.36</v>
       </c>
       <c r="L13" t="n">
-        <v>98.5</v>
+        <v>95.9</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1251,11 +1237,15 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13"/>
+      <c r="Q13" t="n">
+        <v>20000</v>
+      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13"/>
+      <c r="S13" t="n">
+        <v>20000</v>
+      </c>
       <c r="T13"/>
     </row>
   </sheetData>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -110,18 +110,18 @@
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
+    <t xml:space="preserve">canterburybulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">newcastleknights</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">canterburybulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
-  </si>
-  <si>
     <t xml:space="preserve">nqcowboys</t>
   </si>
   <si>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
+    <t xml:space="preserve">stgeorgeillawarradragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St George-Illawarra Dragons</t>
+  </si>
+  <si>
     <t xml:space="preserve">cronullasharks</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stgeorgeillawarradragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St George-Illawarra Dragons</t>
   </si>
 </sst>
 </file>
@@ -570,19 +570,19 @@
         <v>8.7</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6</v>
+        <v>8.7</v>
       </c>
       <c r="F2" t="n">
-        <v>96.4</v>
+        <v>96.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>28.13</v>
+        <v>32.36</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -595,22 +595,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>24.7</v>
+        <v>26.3</v>
       </c>
       <c r="O2" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="P2" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>31.4</v>
+        <v>32.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="T2"/>
     </row>
@@ -631,16 +631,16 @@
         <v>9.3</v>
       </c>
       <c r="F3" t="n">
-        <v>99.9</v>
+        <v>99.8</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>689.66</v>
+        <v>588.24</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -653,22 +653,22 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>71.4</v>
+        <v>70.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>55.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q3" t="n">
         <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="T3"/>
     </row>
@@ -683,22 +683,22 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="E4" t="n">
         <v>6.8</v>
       </c>
       <c r="F4" t="n">
-        <v>55.4</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>44.6</v>
+        <v>42</v>
       </c>
       <c r="I4" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="J4" t="n">
         <v>99.8</v>
@@ -713,22 +713,22 @@
         <v>555.56</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>227.27</v>
+        <v>219.78</v>
       </c>
       <c r="P4" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="R4" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="S4" t="n">
-        <v>6.26</v>
+        <v>6.12</v>
       </c>
       <c r="T4"/>
     </row>
@@ -749,16 +749,16 @@
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>67.7</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="H5" t="n">
-        <v>32.4</v>
+        <v>34</v>
       </c>
       <c r="I5" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -771,22 +771,22 @@
       </c>
       <c r="M5"/>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>43.48</v>
+        <v>50</v>
       </c>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="R5" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="S5" t="n">
-        <v>9.06</v>
+        <v>9.76</v>
       </c>
       <c r="T5"/>
     </row>
@@ -828,25 +828,25 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>555.56</v>
+        <v>500</v>
       </c>
       <c r="N6" t="n">
         <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>86.96</v>
+        <v>93.9</v>
       </c>
       <c r="P6" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q6" t="n">
         <v>4.84</v>
       </c>
       <c r="R6" t="n">
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="S6" t="n">
-        <v>10.76</v>
+        <v>10.92</v>
       </c>
       <c r="T6"/>
     </row>
@@ -861,52 +861,52 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F7" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="G7" t="n">
-        <v>7.02</v>
+        <v>7.75</v>
       </c>
       <c r="H7" t="n">
-        <v>85.8</v>
+        <v>87.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="J7" t="n">
-        <v>97.6</v>
+        <v>97.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="M7" t="n">
-        <v>42.19</v>
+        <v>34.84</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2857.14</v>
+        <v>4000</v>
       </c>
       <c r="P7" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.85</v>
+        <v>12.99</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
-        <v>31.75</v>
+        <v>35.46</v>
       </c>
       <c r="T7"/>
     </row>
@@ -921,50 +921,50 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>26.14</v>
+        <v>42.37</v>
       </c>
       <c r="H8" t="n">
-        <v>96.2</v>
+        <v>97.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="J8" t="n">
-        <v>83.7</v>
+        <v>81.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="L8" t="n">
-        <v>16.3</v>
+        <v>18.6</v>
       </c>
       <c r="M8" t="n">
-        <v>6.14</v>
+        <v>5.39</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.39</v>
+        <v>28.29</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>74.63</v>
+        <v>74.91</v>
       </c>
       <c r="T8"/>
     </row>
@@ -979,50 +979,50 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>49.14</v>
+        <v>28.09</v>
       </c>
       <c r="H9" t="n">
-        <v>98</v>
+        <v>96.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="J9" t="n">
-        <v>79.5</v>
+        <v>82.6</v>
       </c>
       <c r="K9" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="L9" t="n">
-        <v>20.5</v>
+        <v>17.4</v>
       </c>
       <c r="M9" t="n">
-        <v>4.88</v>
+        <v>5.75</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>33.11</v>
+        <v>26.77</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>91.74</v>
+        <v>74.91</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1053,16 +1053,16 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="L10" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1072,13 +1072,13 @@
         <v>0.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1052.63</v>
+        <v>952.38</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>6666.67</v>
+        <v>5000</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1093,10 +1093,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4</v>
+        <v>9.2</v>
       </c>
       <c r="K11" t="n">
-        <v>13.47</v>
+        <v>10.86</v>
       </c>
       <c r="L11" t="n">
-        <v>92.6</v>
+        <v>90.8</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1128,13 +1128,13 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5000</v>
+        <v>2857.14</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1149,10 +1149,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>14.03</v>
+        <v>27.66</v>
       </c>
       <c r="L12" t="n">
-        <v>92.9</v>
+        <v>96.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1184,12 +1184,14 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6666.67</v>
+        <v>20000</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12"/>
+      <c r="S12" t="n">
+        <v>20000</v>
+      </c>
       <c r="T12"/>
     </row>
     <row r="13">
@@ -1203,10 +1205,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1219,16 +1221,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="K13" t="n">
-        <v>24.36</v>
+        <v>18.67</v>
       </c>
       <c r="L13" t="n">
-        <v>95.9</v>
+        <v>94.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1238,14 +1240,12 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
-        <v>20000</v>
-      </c>
+      <c r="S13"/>
       <c r="T13"/>
     </row>
   </sheetData>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -573,16 +573,16 @@
         <v>8.7</v>
       </c>
       <c r="F2" t="n">
-        <v>96.9</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
         <v>1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>32.36</v>
+        <v>32.95</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -595,22 +595,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P2" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="T2"/>
     </row>
@@ -653,13 +653,13 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>70.1</v>
+        <v>69.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.81</v>
@@ -668,7 +668,7 @@
         <v>26.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="T3"/>
     </row>
@@ -689,16 +689,16 @@
         <v>6.8</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>58.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>99.8</v>
@@ -710,25 +710,25 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>555.56</v>
+        <v>588.24</v>
       </c>
       <c r="N4" t="n">
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>219.78</v>
+        <v>217.39</v>
       </c>
       <c r="P4" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="R4" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="S4" t="n">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="T4"/>
     </row>
@@ -749,16 +749,16 @@
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H5" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -777,16 +777,16 @@
         <v>50</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="R5" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S5" t="n">
-        <v>9.76</v>
+        <v>9.73</v>
       </c>
       <c r="T5"/>
     </row>
@@ -807,16 +807,16 @@
         <v>7.3</v>
       </c>
       <c r="F6" t="n">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H6" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>99.8</v>
@@ -828,25 +828,25 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>500</v>
+        <v>476.19</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>93.9</v>
+        <v>96.15</v>
       </c>
       <c r="P6" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.84</v>
+        <v>4.94</v>
       </c>
       <c r="R6" t="n">
-        <v>9.2</v>
+        <v>8.9</v>
       </c>
       <c r="S6" t="n">
-        <v>10.92</v>
+        <v>11.23</v>
       </c>
       <c r="T6"/>
     </row>
@@ -867,28 +867,28 @@
         <v>5.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="G7" t="n">
-        <v>7.75</v>
+        <v>8.06</v>
       </c>
       <c r="H7" t="n">
-        <v>87.1</v>
+        <v>87.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="J7" t="n">
-        <v>97.1</v>
+        <v>96.9</v>
       </c>
       <c r="K7" t="n">
         <v>1.03</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>34.84</v>
+        <v>32.52</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -897,16 +897,16 @@
         <v>4000</v>
       </c>
       <c r="P7" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.99</v>
+        <v>13.87</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="S7" t="n">
-        <v>35.46</v>
+        <v>38.83</v>
       </c>
       <c r="T7"/>
     </row>
@@ -927,44 +927,44 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>42.37</v>
+        <v>39.92</v>
       </c>
       <c r="H8" t="n">
-        <v>97.6</v>
+        <v>97.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J8" t="n">
-        <v>81.4</v>
+        <v>81.9</v>
       </c>
       <c r="K8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="L8" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="M8" t="n">
-        <v>5.39</v>
+        <v>5.53</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.29</v>
+        <v>26.88</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>74.91</v>
+        <v>69.93</v>
       </c>
       <c r="T8"/>
     </row>
@@ -988,7 +988,7 @@
         <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>28.09</v>
+        <v>27.4</v>
       </c>
       <c r="H9" t="n">
         <v>96.4</v>
@@ -997,32 +997,32 @@
         <v>1.04</v>
       </c>
       <c r="J9" t="n">
-        <v>82.6</v>
+        <v>82.5</v>
       </c>
       <c r="K9" t="n">
         <v>1.21</v>
       </c>
       <c r="L9" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="M9" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.77</v>
+        <v>26.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>74.91</v>
+        <v>76.05</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1053,13 +1053,13 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.76</v>
+        <v>4.66</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.27</v>
@@ -1072,7 +1072,7 @@
         <v>0.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>952.38</v>
+        <v>800</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1109,13 +1109,13 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="K11" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>90.8</v>
+        <v>90.9</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2857.14</v>
+        <v>2500</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>27.66</v>
+        <v>29.99</v>
       </c>
       <c r="L12" t="n">
-        <v>96.4</v>
+        <v>96.7</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>2.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1221,16 +1221,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K13" t="n">
-        <v>18.67</v>
+        <v>19.29</v>
       </c>
       <c r="L13" t="n">
-        <v>94.6</v>
+        <v>94.8</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -86,28 +86,40 @@
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">canberraraiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weststigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wests Tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weststigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wests Tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberraraiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
+    <t xml:space="preserve">nqcowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Queensland Cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
     <t xml:space="preserve">canterburybulldogs</t>
@@ -116,34 +128,22 @@
     <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nqcowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Queensland Cowboys</t>
-  </si>
-  <si>
     <t xml:space="preserve">parramattaeels</t>
   </si>
   <si>
     <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
+    <t xml:space="preserve">cronullasharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronullasharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
   </si>
 </sst>
 </file>
@@ -564,25 +564,25 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7</v>
+        <v>8.9</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7</v>
+        <v>8.9</v>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>99.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>32.95</v>
+        <v>229.89</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -595,22 +595,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>26.7</v>
+        <v>22.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.74</v>
+        <v>4.47</v>
       </c>
       <c r="P2" t="n">
-        <v>56.8</v>
+        <v>57.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>32.6</v>
+        <v>34.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="T2"/>
     </row>
@@ -622,7 +622,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>9.3</v>
@@ -631,17 +631,15 @@
         <v>9.3</v>
       </c>
       <c r="F3" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>588.24</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3"/>
       <c r="J3" t="n">
         <v>100</v>
       </c>
@@ -653,22 +651,22 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>69.8</v>
+        <v>76.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>55.3</v>
+        <v>57.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="S3" t="n">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="T3"/>
     </row>
@@ -680,55 +678,53 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="E4" t="n">
         <v>6.8</v>
       </c>
       <c r="F4" t="n">
-        <v>58.4</v>
+        <v>82.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="H4" t="n">
-        <v>41.6</v>
+        <v>17.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>5.65</v>
       </c>
       <c r="J4" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>588.24</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M4"/>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O4" t="n">
-        <v>217.39</v>
+        <v>243.9</v>
       </c>
       <c r="P4" t="n">
-        <v>29.8</v>
+        <v>36.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.36</v>
+        <v>2.77</v>
       </c>
       <c r="R4" t="n">
-        <v>16.4</v>
+        <v>20.6</v>
       </c>
       <c r="S4" t="n">
-        <v>6.1</v>
+        <v>4.86</v>
       </c>
       <c r="T4"/>
     </row>
@@ -743,22 +739,22 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="F5" t="n">
-        <v>66.2</v>
+        <v>53.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>33.8</v>
+        <v>46.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.96</v>
+        <v>2.14</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -771,22 +767,22 @@
       </c>
       <c r="M5"/>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>17.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.35</v>
+        <v>5.76</v>
       </c>
       <c r="R5" t="n">
-        <v>10.3</v>
+        <v>6.7</v>
       </c>
       <c r="S5" t="n">
-        <v>9.73</v>
+        <v>14.95</v>
       </c>
       <c r="T5"/>
     </row>
@@ -798,55 +794,53 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="E6" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>57.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>42.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="J6" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>476.19</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M6"/>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>96.15</v>
+        <v>384.62</v>
       </c>
       <c r="P6" t="n">
-        <v>20.2</v>
+        <v>14.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.94</v>
+        <v>7.08</v>
       </c>
       <c r="R6" t="n">
-        <v>8.9</v>
+        <v>4.9</v>
       </c>
       <c r="S6" t="n">
-        <v>11.23</v>
+        <v>20.62</v>
       </c>
       <c r="T6"/>
     </row>
@@ -861,52 +855,50 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>12.4</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>8.06</v>
+        <v>16.63</v>
       </c>
       <c r="H7" t="n">
-        <v>87.6</v>
+        <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="J7" t="n">
-        <v>96.9</v>
+        <v>80.5</v>
       </c>
       <c r="K7" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>19.5</v>
       </c>
       <c r="M7" t="n">
-        <v>32.52</v>
+        <v>5.13</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="n">
-        <v>4000</v>
-      </c>
+      <c r="O7"/>
       <c r="P7" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.87</v>
+        <v>16.31</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>38.83</v>
+        <v>49.14</v>
       </c>
       <c r="T7"/>
     </row>
@@ -921,50 +913,50 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="G8" t="n">
-        <v>39.92</v>
+        <v>377.36</v>
       </c>
       <c r="H8" t="n">
-        <v>97.5</v>
+        <v>99.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>81.9</v>
+        <v>54.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="L8" t="n">
-        <v>18.1</v>
+        <v>45.5</v>
       </c>
       <c r="M8" t="n">
-        <v>5.53</v>
+        <v>2.2</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.88</v>
+        <v>31.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>69.93</v>
+        <v>78.43</v>
       </c>
       <c r="T8"/>
     </row>
@@ -979,50 +971,50 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>27.4</v>
+        <v>104.17</v>
       </c>
       <c r="H9" t="n">
-        <v>96.4</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="J9" t="n">
-        <v>82.5</v>
+        <v>59.8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="L9" t="n">
-        <v>17.5</v>
+        <v>40.2</v>
       </c>
       <c r="M9" t="n">
-        <v>5.7</v>
+        <v>2.49</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>27.89</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>76.05</v>
+        <v>79.37</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1034,51 +1026,53 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10"/>
+        <v>0.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>273.97</v>
+      </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>99.6</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>21.5</v>
+        <v>51.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.66</v>
+        <v>1.93</v>
       </c>
       <c r="L10" t="n">
-        <v>78.5</v>
+        <v>48.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>800</v>
+        <v>39.92</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>99.01</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1090,13 +1084,13 @@
         <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1109,32 +1103,32 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>9.1</v>
+        <v>31.8</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>3.14</v>
       </c>
       <c r="L11" t="n">
-        <v>90.9</v>
+        <v>68.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2500</v>
+        <v>65.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="S11" t="n">
-        <v>10000</v>
+        <v>136.05</v>
       </c>
       <c r="T11"/>
     </row>
@@ -1149,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1165,32 +1159,32 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>29.99</v>
+        <v>5.25</v>
       </c>
       <c r="L12" t="n">
-        <v>96.7</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>20000</v>
+        <v>1111.11</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S12" t="n">
-        <v>20000</v>
+        <v>1818.18</v>
       </c>
       <c r="T12"/>
     </row>
@@ -1205,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>2.5</v>
@@ -1221,16 +1215,16 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>19.29</v>
+        <v>39.45</v>
       </c>
       <c r="L13" t="n">
-        <v>94.8</v>
+        <v>97.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1239,9 +1233,7 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>10000</v>
-      </c>
+      <c r="Q13"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -86,48 +86,54 @@
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">weststigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wests Tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
     <t xml:space="preserve">canberraraiders</t>
   </si>
   <si>
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weststigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wests Tigers</t>
-  </si>
-  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">nqcowboys</t>
   </si>
   <si>
     <t xml:space="preserve">North Queensland Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
     <t xml:space="preserve">canterburybulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
+    <t xml:space="preserve">stgeorgeillawarradragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St George-Illawarra Dragons</t>
+  </si>
+  <si>
     <t xml:space="preserve">parramattaeels</t>
   </si>
   <si>
@@ -138,12 +144,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stgeorgeillawarradragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St George-Illawarra Dragons</t>
   </si>
 </sst>
 </file>
@@ -564,26 +564,24 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>99.6</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>229.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2"/>
       <c r="J2" t="n">
         <v>100</v>
       </c>
@@ -595,22 +593,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>22.4</v>
+        <v>7.8</v>
       </c>
       <c r="O2" t="n">
-        <v>4.47</v>
+        <v>12.85</v>
       </c>
       <c r="P2" t="n">
-        <v>57.8</v>
+        <v>56.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>34.4</v>
+        <v>32.3</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T2"/>
     </row>
@@ -622,13 +620,13 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="E3" t="n">
-        <v>9.3</v>
+        <v>9.6</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -651,22 +649,22 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>76.9</v>
+        <v>92.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>57.6</v>
+        <v>63.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>27.1</v>
+        <v>30.1</v>
       </c>
       <c r="S3" t="n">
-        <v>3.69</v>
+        <v>3.32</v>
       </c>
       <c r="T3"/>
     </row>
@@ -678,25 +676,25 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8</v>
+        <v>8.3</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8</v>
+        <v>8.3</v>
       </c>
       <c r="F4" t="n">
-        <v>82.3</v>
+        <v>97.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="H4" t="n">
-        <v>17.7</v>
+        <v>2.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.65</v>
+        <v>42.02</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
@@ -709,22 +707,20 @@
       </c>
       <c r="M4"/>
       <c r="N4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>243.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4"/>
       <c r="P4" t="n">
-        <v>36.1</v>
+        <v>33.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="R4" t="n">
-        <v>20.6</v>
+        <v>18.1</v>
       </c>
       <c r="S4" t="n">
-        <v>4.86</v>
+        <v>5.51</v>
       </c>
       <c r="T4"/>
     </row>
@@ -736,25 +732,25 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="F5" t="n">
-        <v>53.2</v>
+        <v>82.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.21</v>
       </c>
       <c r="H5" t="n">
-        <v>46.8</v>
+        <v>17.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.14</v>
+        <v>5.71</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -769,20 +765,18 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>5000</v>
-      </c>
+      <c r="O5"/>
       <c r="P5" t="n">
-        <v>17.3</v>
+        <v>18.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.76</v>
+        <v>5.32</v>
       </c>
       <c r="R5" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="S5" t="n">
-        <v>14.95</v>
+        <v>12.76</v>
       </c>
       <c r="T5"/>
     </row>
@@ -794,25 +788,25 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="n">
-        <v>57.3</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>5.28</v>
       </c>
       <c r="H6" t="n">
-        <v>42.7</v>
+        <v>81</v>
       </c>
       <c r="I6" t="n">
-        <v>2.34</v>
+        <v>1.23</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
@@ -825,22 +819,20 @@
       </c>
       <c r="M6"/>
       <c r="N6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>384.62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6"/>
       <c r="P6" t="n">
-        <v>14.1</v>
+        <v>16.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.08</v>
+        <v>6.08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="S6" t="n">
-        <v>20.62</v>
+        <v>13.45</v>
       </c>
       <c r="T6"/>
     </row>
@@ -855,50 +847,50 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>16.63</v>
+        <v>4000</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>80.5</v>
+        <v>91.5</v>
       </c>
       <c r="K7" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="L7" t="n">
-        <v>19.5</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>5.13</v>
+        <v>11.73</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.31</v>
+        <v>22.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
-        <v>49.14</v>
+        <v>60.24</v>
       </c>
       <c r="T7"/>
     </row>
@@ -910,53 +902,53 @@
         <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>377.36</v>
+        <v>109.29</v>
       </c>
       <c r="H8" t="n">
-        <v>99.7</v>
+        <v>99.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J8" t="n">
-        <v>54.5</v>
+        <v>92.2</v>
       </c>
       <c r="K8" t="n">
-        <v>1.84</v>
+        <v>1.08</v>
       </c>
       <c r="L8" t="n">
-        <v>45.5</v>
+        <v>7.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2</v>
+        <v>12.85</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.35</v>
+        <v>23.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>78.43</v>
+        <v>68.03</v>
       </c>
       <c r="T8"/>
     </row>
@@ -971,50 +963,48 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>104.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9"/>
       <c r="H9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>59.8</v>
+        <v>54.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="L9" t="n">
-        <v>40.2</v>
+        <v>45.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>27.89</v>
+        <v>66.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="S9" t="n">
-        <v>79.37</v>
+        <v>131.58</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1029,50 +1019,48 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>273.97</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10"/>
       <c r="H10" t="n">
-        <v>99.6</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>51.8</v>
+        <v>34.8</v>
       </c>
       <c r="K10" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="L10" t="n">
-        <v>48.2</v>
+        <v>65.2</v>
       </c>
       <c r="M10" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.92</v>
+        <v>152.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S10" t="n">
-        <v>99.01</v>
+        <v>344.83</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1087,10 +1075,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1103,33 +1091,29 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>31.8</v>
+        <v>16.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.14</v>
+        <v>6.13</v>
       </c>
       <c r="L11" t="n">
-        <v>68.2</v>
+        <v>83.7</v>
       </c>
       <c r="M11" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>65.36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q11"/>
       <c r="R11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>136.05</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S11"/>
       <c r="T11"/>
     </row>
     <row r="12">
@@ -1140,13 +1124,13 @@
         <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1159,33 +1143,29 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>10.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.25</v>
+        <v>9.36</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>89.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1111.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q12"/>
       <c r="R12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1818.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S12"/>
       <c r="T12"/>
     </row>
     <row r="13">
@@ -1199,10 +1179,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1215,16 +1195,14 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>39.45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13"/>
       <c r="L13" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -104,28 +104,28 @@
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
+    <t xml:space="preserve">canterburybulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">nqcowboys</t>
   </si>
   <si>
     <t xml:space="preserve">North Queensland Cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterburybulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
@@ -567,10 +567,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -593,22 +593,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="O2" t="n">
-        <v>12.85</v>
+        <v>7.42</v>
       </c>
       <c r="P2" t="n">
-        <v>56.8</v>
+        <v>52.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T2"/>
     </row>
@@ -623,10 +623,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9.6</v>
+        <v>9.3</v>
       </c>
       <c r="E3" t="n">
-        <v>9.6</v>
+        <v>9.3</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -649,22 +649,22 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>92.2</v>
+        <v>86.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>63.6</v>
+        <v>55.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>30.1</v>
+        <v>24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.32</v>
+        <v>4.16</v>
       </c>
       <c r="T3"/>
     </row>
@@ -685,16 +685,16 @@
         <v>8.3</v>
       </c>
       <c r="F4" t="n">
-        <v>97.6</v>
+        <v>98.3</v>
       </c>
       <c r="G4" t="n">
         <v>1.02</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>42.02</v>
+        <v>57.31</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
@@ -711,16 +711,16 @@
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
-        <v>33.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>18.1</v>
+        <v>21.2</v>
       </c>
       <c r="S4" t="n">
-        <v>5.51</v>
+        <v>4.73</v>
       </c>
       <c r="T4"/>
     </row>
@@ -741,16 +741,16 @@
         <v>6.7</v>
       </c>
       <c r="F5" t="n">
-        <v>82.5</v>
+        <v>82.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I5" t="n">
-        <v>5.71</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -767,16 +767,16 @@
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="R5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="S5" t="n">
-        <v>12.76</v>
+        <v>11.63</v>
       </c>
       <c r="T5"/>
     </row>
@@ -791,22 +791,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>16.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5.28</v>
+        <v>5.98</v>
       </c>
       <c r="H6" t="n">
-        <v>81</v>
+        <v>83.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
@@ -823,16 +823,16 @@
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.08</v>
+        <v>5.73</v>
       </c>
       <c r="R6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="S6" t="n">
-        <v>13.45</v>
+        <v>13.4</v>
       </c>
       <c r="T6"/>
     </row>
@@ -847,50 +847,50 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4000</v>
+        <v>35.03</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>97.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="J7" t="n">
-        <v>91.5</v>
+        <v>90.3</v>
       </c>
       <c r="K7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.5</v>
+        <v>9.7</v>
       </c>
       <c r="M7" t="n">
-        <v>11.73</v>
+        <v>10.28</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="R7" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q7" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="S7" t="n">
-        <v>60.24</v>
+        <v>22.37</v>
       </c>
       <c r="T7"/>
     </row>
@@ -905,50 +905,50 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>109.29</v>
+        <v>2500</v>
       </c>
       <c r="H8" t="n">
-        <v>99.1</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>92.2</v>
+        <v>90</v>
       </c>
       <c r="K8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>12.85</v>
+        <v>10.02</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.58</v>
+        <v>18.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>68.03</v>
+        <v>47.96</v>
       </c>
       <c r="T8"/>
     </row>
@@ -979,16 +979,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>54.5</v>
+        <v>56.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="L9" t="n">
-        <v>45.5</v>
+        <v>43.8</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>66.67</v>
+        <v>64.72</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S9" t="n">
-        <v>131.58</v>
+        <v>134.23</v>
       </c>
       <c r="T9"/>
     </row>
@@ -1019,10 +1019,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1035,32 +1035,32 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>34.8</v>
+        <v>40.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.87</v>
+        <v>2.46</v>
       </c>
       <c r="L10" t="n">
-        <v>65.2</v>
+        <v>59.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>152.67</v>
+        <v>210.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="S10" t="n">
-        <v>344.83</v>
+        <v>526.32</v>
       </c>
       <c r="T10"/>
     </row>
@@ -1091,16 +1091,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>16.3</v>
+        <v>14.2</v>
       </c>
       <c r="K11" t="n">
-        <v>6.13</v>
+        <v>7.05</v>
       </c>
       <c r="L11" t="n">
-        <v>83.7</v>
+        <v>85.8</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1143,16 +1143,16 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>10.7</v>
+        <v>8.6</v>
       </c>
       <c r="K12" t="n">
-        <v>9.36</v>
+        <v>11.6</v>
       </c>
       <c r="L12" t="n">
-        <v>89.3</v>
+        <v>91.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1197,7 +1197,9 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13"/>
+      <c r="K13" t="n">
+        <v>5000</v>
+      </c>
       <c r="L13" t="n">
         <v>100</v>
       </c>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -80,12 +80,24 @@
     <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastleknights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydneyroosters</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">canberraraiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
     <t xml:space="preserve">weststigers</t>
   </si>
   <si>
@@ -98,18 +110,6 @@
     <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
-    <t xml:space="preserve">canberraraiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastleknights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">North Queensland Cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
+  </si>
+  <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
     <t xml:space="preserve">cronullasharks</t>
@@ -564,13 +564,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -593,22 +593,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>7.42</v>
+        <v>2222.22</v>
       </c>
       <c r="P2" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="R2" t="n">
-        <v>31.2</v>
+        <v>30.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="T2"/>
     </row>
@@ -620,24 +620,24 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.3</v>
+        <v>5.4</v>
       </c>
       <c r="E3" t="n">
-        <v>9.3</v>
+        <v>5.4</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3"/>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3"/>
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
@@ -649,22 +649,20 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O3"/>
       <c r="P3" t="n">
-        <v>55.7</v>
+        <v>43.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="S3" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
       <c r="T3"/>
     </row>
@@ -676,26 +674,24 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>8.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>8.3</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>57.31</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4"/>
       <c r="J4" t="n">
         <v>100</v>
       </c>
@@ -707,20 +703,22 @@
       </c>
       <c r="M4"/>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4"/>
+        <v>100</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
       <c r="P4" t="n">
-        <v>36.3</v>
+        <v>39.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
-        <v>21.2</v>
+        <v>17.9</v>
       </c>
       <c r="S4" t="n">
-        <v>4.73</v>
+        <v>5.57</v>
       </c>
       <c r="T4"/>
     </row>
@@ -732,25 +730,23 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="F5" t="n">
-        <v>82.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.22</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5"/>
       <c r="H5" t="n">
-        <v>17.9</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -767,16 +763,16 @@
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
-        <v>20.2</v>
+        <v>31.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.95</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="S5" t="n">
-        <v>11.63</v>
+        <v>7.94</v>
       </c>
       <c r="T5"/>
     </row>
@@ -788,26 +784,24 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="F6" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>5.98</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I6"/>
       <c r="J6" t="n">
         <v>100</v>
       </c>
@@ -823,16 +817,16 @@
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.73</v>
+        <v>5.4</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="S6" t="n">
-        <v>13.4</v>
+        <v>11.88</v>
       </c>
       <c r="T6"/>
     </row>
@@ -844,53 +838,49 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>35.03</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>97.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.03</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7"/>
       <c r="J7" t="n">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>9.7</v>
-      </c>
-      <c r="M7" t="n">
-        <v>10.28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M7"/>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>10.2</v>
+        <v>15.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.85</v>
+        <v>6.43</v>
       </c>
       <c r="R7" t="n">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="S7" t="n">
-        <v>22.37</v>
+        <v>14.57</v>
       </c>
       <c r="T7"/>
     </row>
@@ -905,17 +895,15 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
-        <v>2500</v>
-      </c>
+      <c r="G8"/>
       <c r="H8" t="n">
         <v>100</v>
       </c>
@@ -923,32 +911,30 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" t="n">
-        <v>10.02</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M8"/>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.96</v>
+        <v>20000</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>47.96</v>
+        <v>20000</v>
       </c>
       <c r="T8"/>
     </row>
@@ -963,10 +949,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -979,33 +965,29 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>56.2</v>
+        <v>54.9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="M9" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>64.72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9"/>
       <c r="R9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>134.23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S9"/>
       <c r="T9"/>
     </row>
     <row r="10">
@@ -1019,10 +1001,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1035,33 +1017,29 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>40.7</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.46</v>
+        <v>44.94</v>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>97.8</v>
       </c>
       <c r="M10" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>210.53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q10"/>
       <c r="R10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>526.32</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S10"/>
       <c r="T10"/>
     </row>
     <row r="11">
@@ -1072,7 +1050,7 @@
         <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>3.5</v>
@@ -1091,16 +1069,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>14.2</v>
+        <v>42.8</v>
       </c>
       <c r="K11" t="n">
-        <v>7.05</v>
+        <v>2.33</v>
       </c>
       <c r="L11" t="n">
-        <v>85.8</v>
+        <v>57.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1127,10 +1105,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1143,16 +1121,14 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12"/>
       <c r="L12" t="n">
-        <v>91.4</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1176,13 +1152,13 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1197,9 +1173,7 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>5000</v>
-      </c>
+      <c r="K13"/>
       <c r="L13" t="n">
         <v>100</v>
       </c>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -593,22 +593,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2222.22</v>
+        <v>1818.18</v>
       </c>
       <c r="P2" t="n">
-        <v>50.7</v>
+        <v>48.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>30.6</v>
+        <v>29.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="T2"/>
     </row>
@@ -623,10 +623,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -653,16 +653,16 @@
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
-        <v>43.8</v>
+        <v>45.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>23.6</v>
+        <v>25.7</v>
       </c>
       <c r="S3" t="n">
-        <v>4.24</v>
+        <v>3.9</v>
       </c>
       <c r="T3"/>
     </row>
@@ -703,22 +703,22 @@
       </c>
       <c r="M4"/>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>99.9</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>39.6</v>
+        <v>38.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="R4" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="S4" t="n">
-        <v>5.57</v>
+        <v>6</v>
       </c>
       <c r="T4"/>
     </row>
@@ -733,10 +733,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -763,16 +763,16 @@
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
-        <v>31.8</v>
+        <v>31.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="R5" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="S5" t="n">
-        <v>7.94</v>
+        <v>8.51</v>
       </c>
       <c r="T5"/>
     </row>
@@ -787,10 +787,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="E6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="F6" t="n">
         <v>100</v>
@@ -817,16 +817,16 @@
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>8.4</v>
+        <v>9.3</v>
       </c>
       <c r="S6" t="n">
-        <v>11.88</v>
+        <v>10.7</v>
       </c>
       <c r="T6"/>
     </row>
@@ -871,16 +871,16 @@
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.43</v>
+        <v>6.3</v>
       </c>
       <c r="R7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>14.57</v>
+        <v>14.2</v>
       </c>
       <c r="T7"/>
     </row>
@@ -965,16 +965,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>54.9</v>
+        <v>62.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>45.1</v>
+        <v>37.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.22</v>
+        <v>2.65</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1001,10 +1001,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1017,13 +1017,13 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>44.94</v>
+        <v>54.05</v>
       </c>
       <c r="L10" t="n">
-        <v>97.8</v>
+        <v>98.2</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
@@ -1053,10 +1053,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1069,16 +1069,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>42.8</v>
+        <v>35.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.33</v>
+        <v>2.79</v>
       </c>
       <c r="L11" t="n">
-        <v>57.2</v>
+        <v>64.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
